--- a/public/exports-from-60-with-coowners/29189676.xlsx
+++ b/public/exports-from-60-with-coowners/29189676.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238126</t>
+          <t xml:space="preserve">311238128</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189676.xlsx
+++ b/public/exports-from-60-with-coowners/29189676.xlsx
@@ -10354,12 +10354,12 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10429,12 +10429,12 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10504,12 +10504,12 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10579,12 +10579,12 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10654,12 +10654,12 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10729,12 +10729,12 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -10804,12 +10804,12 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -13939,7 +13939,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238128</t>
+          <t xml:space="preserve">311238126</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
